--- a/data/trans_orig/IP1012-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1012-Edad-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>249911</t>
+          <t>250018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>248331</t>
+          <t>248391</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253108</t>
+          <t>253112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>500254</t>
+          <t>499900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506287</t>
+          <t>506309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137298</t>
+          <t>137032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264381</t>
+          <t>264510</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189243</t>
+          <t>189436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198975</t>
+          <t>199138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205409</t>
+          <t>205406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>390710</t>
+          <t>391706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>398768</t>
+          <t>398785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>675700</t>
+          <t>675622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>680392</t>
+          <t>680386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>711942</t>
+          <t>711744</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720101</t>
+          <t>720083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1389522</t>
+          <t>1390145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1399628</t>
+          <t>1399743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140462</t>
+          <t>140774</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>286510</t>
+          <t>287041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>231167</t>
+          <t>231160</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>493388</t>
+          <t>494741</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150246</t>
+          <t>150259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155378</t>
+          <t>155621</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307001</t>
+          <t>308514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165485</t>
+          <t>164889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172691</t>
+          <t>172143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177343</t>
+          <t>177339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341281</t>
+          <t>341255</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347996</t>
+          <t>347978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>699257</t>
+          <t>698681</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>706010</t>
+          <t>706006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>737279</t>
+          <t>737697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746262</t>
+          <t>746164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1439472</t>
+          <t>1440256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1450822</t>
+          <t>1450871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>254803</t>
+          <t>254423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>465326</t>
+          <t>465359</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>185520</t>
+          <t>185113</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>374364</t>
+          <t>374354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168956</t>
+          <t>168825</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342878</t>
+          <t>341771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>738470</t>
+          <t>738013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744135</t>
+          <t>744121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1442369</t>
+          <t>1442258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448501</t>
+          <t>1448505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1012-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1012-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5958</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3187</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3604</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5365</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>251733</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>247798</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253107</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>252571</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>250018</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>249601</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>251733</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>248391</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253112</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,89%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>757</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>499900</t>
+          <t>500885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506309</t>
+          <t>506287</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4517</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1293</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4483</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3908</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4553</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140222</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>136998</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140222</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>137032</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>401</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264510</t>
+          <t>265155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2374</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6185</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1375</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4661</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4867</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2374</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6911</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>203675</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>199864</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205411</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>192722</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>189436</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>189230</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>203675</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>199138</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205406</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>591</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391706</t>
+          <t>391648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>398785</t>
+          <t>398766</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10822</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5399</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5643</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2617</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10956</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>13064</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1078</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>717011</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>711878</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>720202</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679012</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>675622</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>680386</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>675378</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>680387</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>717011</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>711744</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>720083</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2093</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1390145</t>
+          <t>1390657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1399743</t>
+          <t>1399781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,107 +2669,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1459</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4816</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1459</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4546</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1459</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4560</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>143861</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>140504</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>145320</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>143861</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>140774</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>145320</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>422</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287041</t>
+          <t>286421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145320</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145320</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145320</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145320</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145320</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,74 +3012,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6211</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3316</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3313</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7130</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>265052</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>260890</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>233820</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>231160</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>231163</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>98,59%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>265052</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>259971</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>705</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>494741</t>
+          <t>493575</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3360,102 +3360,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4575</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2950</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5569</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1549</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4891</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157937</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155234</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>153919</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>150259</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>150226</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,02%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157937</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>155621</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>446</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308514</t>
+          <t>307836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5108</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1672</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6448</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5998</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5814</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>176027</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>172849</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>177340</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>169665</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>164889</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>165339</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,02%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>176027</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>172143</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>177339</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>500</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341255</t>
+          <t>341250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347978</t>
+          <t>347983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11838</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3243</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8247</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,13%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6072</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11252</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742877</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>737111</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>746228</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>703685</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698681</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>706006</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>699189</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>706005</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,87%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742877</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>737697</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>746164</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2073</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1440256</t>
+          <t>1439551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1450871</t>
+          <t>1450743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748949</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748949</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748949</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748949</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748949</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748949</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,92 +4959,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3256</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3638</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>257415</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>254805</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>257415</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>254423</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>711</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>465359</t>
+          <t>465328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,107 +5302,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>618</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3459</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3092</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>187954</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>185447</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>187954</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>185113</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>534</t>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>374354</t>
+          <t>374379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1472</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5223</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5577</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>172576</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>169598</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>172576</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>168825</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>478</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341771</t>
+          <t>342123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,92 +5988,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6647</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>2736</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6831</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742108</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>738197</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744133</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742108</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>738013</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744121</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2121</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1442258</t>
+          <t>1442525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448505</t>
+          <t>1448503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
